--- a/data/jogadores_carreiras.xlsx
+++ b/data/jogadores_carreiras.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jogadores" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passagens" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desempenho Competição" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conquistas Passagem" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conquistas Jogador" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Jogadores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Passagens" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Desempenho Competição" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Conquistas Passagem" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Conquistas Jogador" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Checks" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Jogadores'!$A$1:$M$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conquistas Jogador'!$A$1:$E$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conquistas Jogador'!$A$1:$E$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Checks'!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -845,22 +845,22 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76 gols, Eredivisie, KNVB e Europa League — três taças europeias.</t>
+          <t>113 gols, Champions League, Bola de Ouro. A consagração total.</t>
         </is>
       </c>
     </row>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>25</v>
-      </c>
       <c r="J19" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31 jogos pela seleção — e campeão do mundo.</t>
+          <t>39 jogos — e campeão do mundo.</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-2</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2016,97 +2016,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Seleção</t>
+          <t>Clube</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
+          <t>pages/clubes/guarita-fonseca-napoli.html</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Titular na Copa do Mundo campeã — e a história mal começou.</t>
+          <t>Primeira experiência na Serie A e Europa League italiana.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>guarita-fonseca-bolivia-3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Clube</t>
+          <t>Seleção</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
+          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Estreia profissional e artilharia imediata na Copa Boliviana.</t>
+          <t>Titular na Copa do Mundo campeã — e a história mal começou.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2120,16 +2120,16 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2138,29 +2138,29 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-corinthians.html</t>
+          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
+          <t>Estreia profissional e artilharia imediata na Copa Boliviana.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2192,81 +2192,135 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="I24" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="J24" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="J24" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-marseille.html</t>
+          <t>pages/clubes/moreno-escobar-corinthians.html</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Primeira experiência europeia com gols na Ligue 1 e na Europa League.</t>
+          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Clube</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>pages/clubes/moreno-escobar-marseille.html</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Ligue 1 conquistada, 53 gols e três prêmios individuais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>moreno-escobar</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Moreno Escobar</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Bolívia</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Bolívia</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Seleção</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I25" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="I26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>pages/clubes/moreno-escobar-bolivia.html</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Artilheiro da Copa do Mundo — 13 gols no torneio que mudou tudo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L25"/>
+  <autoFilter ref="A1:L26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2277,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4871,7 +4925,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-2</t>
+          <t>guarita-fonseca-bolivia-3</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4902,7 +4956,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-2</t>
+          <t>guarita-fonseca-bolivia-3</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4921,19 +4975,19 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-2</t>
+          <t>guarita-fonseca-bolivia-3</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4964,7 +5018,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4974,28 +5028,28 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5005,19 +5059,19 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Coppa Italia</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>2</v>
@@ -5026,7 +5080,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5036,115 +5090,115 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Eliminatórias</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Copa América</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F91" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G91" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F92" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F92" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G92" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
@@ -5165,23 +5219,23 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Eliminatórias</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F93" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="G93" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5191,28 +5245,28 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Copa América</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>118</v>
+        <v>2</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5222,28 +5276,28 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5253,22 +5307,22 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -5289,23 +5343,23 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5315,28 +5369,28 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5346,28 +5400,28 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5377,28 +5431,28 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5408,28 +5462,28 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5439,19 +5493,19 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>2</v>
@@ -5460,7 +5514,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5470,121 +5524,121 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G103" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5594,28 +5648,28 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Eliminatórias</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>9</v>
+        <v>85</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5625,28 +5679,28 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Copa América</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5656,28 +5710,28 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5687,19 +5741,19 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>11</v>
@@ -5708,7 +5762,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-3</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5718,28 +5772,28 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Eliminatórias</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-3</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5749,28 +5803,28 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Copa América</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-3</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5780,57 +5834,181 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G113" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>salazar-bolivia-3</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Copa do Mundo</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
           <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Salazar</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Oriente Petrolero</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Copa Boliviana</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Liga Boliviana</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sul-Americana</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F114" s="2" t="n">
+      <c r="F118" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G114" s="2" t="n">
+      <c r="G118" s="2" t="n">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G114"/>
+  <autoFilter ref="A1:G118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5841,12 +6019,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="39" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -7507,7 +7685,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-2</t>
+          <t>guarita-fonseca-bolivia-3</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7867,7 +8045,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -7877,17 +8055,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
@@ -7897,27 +8075,27 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Melhor da Ligue 1</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -7927,27 +8105,27 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Artilheiro da Ligue 1</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -7957,27 +8135,27 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Artilheiro da Copa da França</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
@@ -7987,17 +8165,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8007,7 +8185,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Eredivisie</t>
+          <t>Artilheiro da Copa Boliviana</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
@@ -8032,16 +8210,16 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Eredivisie</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -8062,12 +8240,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Melhor da KNVB Beker</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
@@ -8077,7 +8255,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -8087,7 +8265,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -8097,7 +8275,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
@@ -8107,7 +8285,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -8117,7 +8295,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -8127,17 +8305,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -8147,7 +8325,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -8157,15 +8335,105 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Johan Cruijff Schaal</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>salazar-bolivia-3</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Copa do Mundo</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Liga Boliviana</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Copa Boliviana</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F77"/>
+  <autoFilter ref="A1:F80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8176,7 +8444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10285,7 +10553,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -10356,7 +10624,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
@@ -10376,12 +10644,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Johan Cruijff Schaal</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
@@ -10401,12 +10669,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Eredivisie</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
@@ -10431,11 +10699,11 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Eredivisie</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -10456,7 +10724,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Melhor da KNVB Beker</t>
+          <t>Melhor da Eredivisie</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
@@ -10466,22 +10734,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Artilheiro da Eredivisie</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -10491,22 +10759,22 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Melhor da KNVB Beker</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
@@ -10516,12 +10784,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -10531,22 +10799,22 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Bola de Ouro</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -10556,7 +10824,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -10566,12 +10834,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -10581,36 +10849,36 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -10631,7 +10899,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
@@ -10651,16 +10919,16 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -10676,16 +10944,16 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Melhor do Brasileirão</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -10701,16 +10969,16 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro do Brasileirão</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -10726,16 +10994,16 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Copa do Brasil</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -10756,11 +11024,11 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa do Brasil</t>
+          <t>Artilheiro da Copa Boliviana</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -10781,15 +11049,190 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>Melhor do Brasileirão</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro do Brasileirão</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Melhor da Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Melhor da Ligue 1</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Ligue 1</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa da França</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
           <t>Artilheiro da Copa do Mundo</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n">
+      <c r="E111" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E104"/>
+  <autoFilter ref="A1:E111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10997,35 +11440,35 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Total real aplicado</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11036,28 +11479,28 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -11075,28 +11518,28 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>

--- a/data/jogadores_carreiras.xlsx
+++ b/data/jogadores_carreiras.xlsx
@@ -18,10 +18,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Jogadores'!$A$1:$M$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conquistas Jogador'!$A$1:$E$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conquistas Jogador'!$A$1:$E$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Checks'!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0</v>
@@ -782,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -845,22 +845,22 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -890,10 +890,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113 gols, Champions League, Bola de Ouro. A consagração total.</t>
+          <t>153 gols, mais ta?as pelo Ajax e presen?a constante na elite europeia.</t>
         </is>
       </c>
     </row>
@@ -1922,14 +1922,14 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="J19" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>27</v>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
           <t>pages/clubes/salazar-bolivia.html</t>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39 jogos — e campeão do mundo.</t>
+          <t>61 jogos pela sele??o, com mais uma Copa Am?rica no curr?culo.</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-3</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2070,97 +2070,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Seleção</t>
+          <t>Clube</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
+          <t>pages/clubes/guarita-fonseca-marseille.html</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Titular na Copa do Mundo campeã — e a história mal começou.</t>
+          <t>57 jogos, Champions League e Bola de Ouro.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Clube</t>
+          <t>Seleção</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
+          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Estreia profissional e artilharia imediata na Copa Boliviana.</t>
+          <t>Titular na Copa do Mundo campeã — e a história mal começou.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2192,29 +2192,29 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-corinthians.html</t>
+          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
+          <t>Estreia profissional e artilharia imediata na Copa Boliviana.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2228,16 +2228,16 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2246,81 +2246,135 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-marseille.html</t>
+          <t>pages/clubes/moreno-escobar-corinthians.html</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1 conquistada, 53 gols e três prêmios individuais.</t>
+          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Clube</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>pages/clubes/moreno-escobar-marseille.html</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>101 gols, Champions League e dominio completo na Franca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>moreno-escobar</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Moreno Escobar</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Bolívia</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Bolívia</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Seleção</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>pages/clubes/moreno-escobar-bolivia.html</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Artilheiro da Copa do Mundo — 13 gols no torneio que mudou tudo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:L27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2331,10 +2385,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="39" customWidth="1" min="4" max="4"/>
@@ -4925,7 +4979,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-3</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4940,23 +4994,23 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Eliminatórias</t>
+          <t>Eliminat?rias</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-3</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4971,23 +5025,23 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Copa Am?rica</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-3</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5002,23 +5056,23 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5028,28 +5082,28 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5059,28 +5113,28 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Coppa Italia</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5090,28 +5144,28 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F89" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G89" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5121,28 +5175,28 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5152,28 +5206,28 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5183,143 +5237,143 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F92" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F92" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="G92" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Eliminatórias</t>
+          <t>Coppa Italia</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Copa América</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>2</v>
@@ -5328,38 +5382,38 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>118</v>
+        <v>2</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5369,28 +5423,28 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Eliminat?rias</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5400,28 +5454,28 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Copa Am?rica</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5431,28 +5485,28 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5462,28 +5516,28 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5493,28 +5547,28 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5524,28 +5578,28 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5555,28 +5609,28 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5586,28 +5640,28 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5617,100 +5671,100 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5719,29 +5773,29 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -5750,112 +5804,112 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Eliminatórias</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F111" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F111" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="G111" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Copa América</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5865,28 +5919,28 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5896,28 +5950,28 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>13</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5927,28 +5981,28 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5958,57 +6012,336 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>salazar-ajax-2</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Mundial de Clubes</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>salazar-ajax-2</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruijff Schaal</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>salazar-bolivia-3</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Eliminat?rias</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>salazar-bolivia-3</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Copa Am?rica</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>salazar-bolivia-3</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Amistosos</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>salazar-bolivia-3</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Copa do Mundo</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Salazar</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Oriente Petrolero</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Copa Boliviana</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Liga Boliviana</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sul-Americana</t>
         </is>
       </c>
-      <c r="E118" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F118" s="2" t="n">
+      <c r="F127" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G118" s="2" t="n">
+      <c r="G127" s="2" t="n">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G118"/>
+  <autoFilter ref="A1:G127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6019,10 +6352,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -7685,7 +8018,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-3</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -7715,7 +8048,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -7725,7 +8058,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7735,7 +8068,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
@@ -7745,7 +8078,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7755,37 +8088,37 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7795,7 +8128,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
@@ -7805,27 +8138,27 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa do Mundo</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
@@ -7835,27 +8168,27 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Melhor Jogador da Ligue 1</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -7865,57 +8198,57 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Melhor Jogador da Copa da França</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Bola de Ouro</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
@@ -7925,47 +8258,47 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Melhor do Brasileirão</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -7975,7 +8308,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro do Brasileirão</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
@@ -7985,7 +8318,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7995,27 +8328,27 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Copa do Brasil</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -8025,7 +8358,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8035,17 +8368,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa do Brasil</t>
+          <t>Artilheiro da Copa do Mundo</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -8055,7 +8388,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8065,7 +8398,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
@@ -8075,7 +8408,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -8085,27 +8418,27 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Ligue 1</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -8115,17 +8448,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Ligue 1</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -8135,7 +8468,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -8145,7 +8478,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8155,17 +8488,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa da França</t>
+          <t>Melhor do Brasileirão</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -8175,7 +8508,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8185,37 +8518,37 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Artilheiro do Brasileirão</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Melhor da Copa do Brasil</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
@@ -8225,47 +8558,47 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Artilheiro da Copa do Brasil</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -8275,27 +8608,27 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -8305,7 +8638,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
@@ -8315,17 +8648,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -8335,7 +8668,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruijff Schaal</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
@@ -8345,17 +8678,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -8365,7 +8698,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
@@ -8375,65 +8708,395 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Melhor da Ligue 1</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Ligue 1</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa da França</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar-the-strongest-1</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa Boliviana</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>salazar-ajax-2</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>salazar-ajax-2</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>KNVB Beker</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>salazar-ajax-2</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>salazar-ajax-2</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>salazar-ajax-2</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruijff Schaal</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>salazar-ajax-2</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Mundial</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>salazar-bolivia-3</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Copa do Mundo</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
           <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Salazar</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Oriente Petrolero</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Título coletivo</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Liga Boliviana</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Copa Boliviana</t>
         </is>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F91" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F80"/>
+  <autoFilter ref="A1:F91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8444,7 +9107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10553,7 +11216,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -10578,7 +11241,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -10653,7 +11316,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -10694,16 +11357,16 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -10724,11 +11387,11 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Eredivisie</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -10749,11 +11412,11 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Eredivisie</t>
+          <t>Melhor da Eredivisie</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -10774,7 +11437,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Melhor da KNVB Beker</t>
+          <t>Artilheiro da Eredivisie</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
@@ -10799,32 +11462,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Bola de Ouro</t>
+          <t>Melhor da KNVB Beker</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Bola de Ouro</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -10849,7 +11512,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -10869,27 +11532,27 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -10899,7 +11562,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
@@ -10909,12 +11572,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -10924,22 +11587,22 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -10949,7 +11612,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
@@ -10959,12 +11622,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -10974,7 +11637,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
@@ -10984,37 +11647,37 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -11024,7 +11687,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Melhor Jogador da Ligue 1</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
@@ -11034,12 +11697,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -11049,22 +11712,22 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Melhor do Brasileirão</t>
+          <t>Melhor Jogador da Copa da França</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -11074,11 +11737,11 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro do Brasileirão</t>
+          <t>Bola de Ouro</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -11094,16 +11757,16 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Copa do Brasil</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -11119,12 +11782,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa do Brasil</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
@@ -11144,12 +11807,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Ligue 1</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
@@ -11169,16 +11832,16 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Ligue 1</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -11194,12 +11857,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa da França</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
@@ -11219,20 +11882,295 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Copa da França</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Copa do Mundo</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
           <t>Prêmio individual</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa Boliviana</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Melhor do Brasileirão</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro do Brasileirão</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Melhor da Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Melhor da Ligue 1</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Ligue 1</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa da França</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Artilheiro da Copa do Mundo</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n">
+      <c r="E122" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E111"/>
+  <autoFilter ref="A1:E122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11440,28 +12378,28 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -11479,28 +12417,28 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -11518,28 +12456,28 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>

--- a/data/jogadores_carreiras.xlsx
+++ b/data/jogadores_carreiras.xlsx
@@ -18,10 +18,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Jogadores'!$A$1:$M$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conquistas Jogador'!$A$1:$E$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conquistas Jogador'!$A$1:$E$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Checks'!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>351</v>
+        <v>404</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>351</v>
+        <v>404</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0</v>
@@ -782,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>5</v>
@@ -845,22 +845,22 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1883,14 +1883,14 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>153 gols, mais ta?as pelo Ajax e presen?a constante na elite europeia.</t>
+          <t>153 gols, mais taças pelo Ajax e presença constante na elite europeia.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-torino-3</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1908,97 +1908,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Seleção</t>
+          <t>Clube</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/salazar-bolivia.html</t>
+          <t>pages/clubes/salazar-torino.html</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61 jogos pela sele??o, com mais uma Copa Am?rica no curr?culo.</t>
+          <t>53 jogos, Supercopa da Itália e Europa League.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Clube</t>
+          <t>Seleção</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-potosi.html</t>
+          <t>pages/clubes/salazar-bolivia.html</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81 jogos, Liga Boliviana conquistada e dois prêmios de melhor jogador.</t>
+          <t>61 jogos pela seleção, com mais uma Copa América no currículo.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2012,16 +2012,16 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2030,29 +2030,29 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-napoli.html</t>
+          <t>pages/clubes/guarita-fonseca-potosi.html</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Primeira experiência na Serie A e Europa League italiana.</t>
+          <t>81 jogos, Liga Boliviana conquistada e dois prêmios de melhor jogador.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2066,16 +2066,16 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2084,29 +2084,29 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-marseille.html</t>
+          <t>pages/clubes/guarita-fonseca-napoli.html</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57 jogos, Champions League e Bola de Ouro.</t>
+          <t>Primeira experi?ncia na Serie A e Europa League italiana.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-4</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2120,101 +2120,101 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Seleção</t>
+          <t>Clube</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
+          <t>pages/clubes/guarita-fonseca-marseille.html</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Titular na Copa do Mundo campeã — e a história mal começou.</t>
+          <t>103 jogos, domínio francês, Champions League e Bola de Ouro.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Clube</t>
+          <t>Seleção</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
+          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Estreia profissional e artilharia imediata na Copa Boliviana.</t>
+          <t>Titular na Copa do Mundo campe? ? e a história mal come?ou.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2228,16 +2228,16 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2246,29 +2246,29 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-corinthians.html</t>
+          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
+          <t>Estreia profissional e artilharia imediata na Copa Boliviana.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2282,16 +2282,16 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2300,81 +2300,135 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-marseille.html</t>
+          <t>pages/clubes/moreno-escobar-corinthians.html</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101 gols, Champions League e dominio completo na Franca.</t>
+          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Clube</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>pages/clubes/moreno-escobar-marseille.html</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>181 gols, Champions League, Mundial e domínio completo na França.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>moreno-escobar</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Moreno Escobar</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Bolívia</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Bolívia</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Seleção</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="J28" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>pages/clubes/moreno-escobar-bolivia.html</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Artilheiro da Copa do Mundo — 13 gols no torneio que mudou tudo.</t>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa do Mundo ? 13 gols no torneio que mudou tudo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L27"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2385,7 +2439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4994,7 +5048,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Eliminat?rias</t>
+          <t>Eliminatórias</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -5025,7 +5079,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Copa Am?rica</t>
+          <t>Copa América</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -5122,13 +5176,13 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89">
@@ -5153,13 +5207,13 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -5184,13 +5238,13 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F90" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -5215,19 +5269,19 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5237,22 +5291,22 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Supercopa da Europa</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5273,17 +5327,17 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Coppa Italia</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -5304,23 +5358,23 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Coppa Italia</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5330,22 +5384,22 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -5366,17 +5420,17 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97">
@@ -5397,48 +5451,48 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F97" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Eliminat?rias</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
@@ -5459,17 +5513,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Copa Am?rica</t>
+          <t>Eliminatórias</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F99" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G99" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -5490,17 +5544,17 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Copa América</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -5521,23 +5575,23 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5547,22 +5601,22 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -5583,17 +5637,17 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -5614,17 +5668,17 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -5645,23 +5699,23 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5671,22 +5725,22 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -5707,17 +5761,17 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
@@ -5738,17 +5792,17 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -5769,17 +5823,17 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -5800,23 +5854,23 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5826,28 +5880,28 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5857,22 +5911,22 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Mundial de Clubes</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5893,79 +5947,79 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G113" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -5986,17 +6040,17 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>19</v>
+        <v>133</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
     </row>
     <row r="117">
@@ -6017,17 +6071,17 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
@@ -6048,17 +6102,17 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Mundial de Clubes</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
@@ -6079,23 +6133,23 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruijff Schaal</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6105,28 +6159,28 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Eliminat?rias</t>
+          <t>Mundial de Clubes</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6136,28 +6190,28 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Copa Am?rica</t>
+          <t>Johan Cruijff Schaal</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6172,23 +6226,23 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Eliminatórias</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6203,23 +6257,23 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Copa América</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F123" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F123" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="G123" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6229,28 +6283,28 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6260,22 +6314,22 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
@@ -6296,17 +6350,17 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
@@ -6327,21 +6381,207 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
+          <t>Liga Boliviana</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
           <t>Sul-Americana</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F127" s="2" t="n">
+      <c r="F129" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G127" s="2" t="n">
+      <c r="G129" s="2" t="n">
         <v>7</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Copa da Itália (Coppa Italia)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Supercopa da Itália</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G127"/>
+  <autoFilter ref="A1:G133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6352,7 +6592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -8072,7 +8312,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -8098,11 +8338,11 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -8128,11 +8368,11 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -8162,7 +8402,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -8183,12 +8423,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Melhor Jogador da Ligue 1</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -8213,12 +8453,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Melhor Jogador da Copa da França</t>
+          <t>Supercopa da Europa</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
@@ -8248,7 +8488,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Bola de Ouro</t>
+          <t>Melhor Jogador da Ligue 1</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
@@ -8258,7 +8498,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -8268,17 +8508,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Melhor Jogador da Copa da França</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
@@ -8288,7 +8528,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -8298,7 +8538,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8308,27 +8548,27 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Bola de Ouro</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8338,7 +8578,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
@@ -8348,17 +8588,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8368,17 +8608,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa do Mundo</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -8388,7 +8628,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8398,7 +8638,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
@@ -8408,7 +8648,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -8418,21 +8658,21 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Artilheiro da Copa do Mundo</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -8458,7 +8698,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -8483,12 +8723,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Melhor do Brasileirão</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
@@ -8513,16 +8753,16 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro do Brasileirão</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -8548,7 +8788,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Copa do Brasil</t>
+          <t>Melhor do Brasileirão</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
@@ -8578,7 +8818,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa do Brasil</t>
+          <t>Artilheiro do Brasileirão</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
@@ -8588,7 +8828,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -8598,17 +8838,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Melhor da Copa do Brasil</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
@@ -8618,7 +8858,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -8628,21 +8868,21 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Artilheiro da Copa do Brasil</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -8668,11 +8908,11 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -8698,7 +8938,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
@@ -8723,12 +8963,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Ligue 1</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
@@ -8753,16 +8993,16 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Ligue 1</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8788,17 +9028,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa da França</t>
+          <t>Melhor da Ligue 1</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -8808,7 +9048,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -8818,71 +9058,71 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Artilheiro da Ligue 1</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Artilheiro da Copa da França</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Artilheiro da Copa Boliviana</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -8908,11 +9148,11 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -8938,11 +9178,11 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -8968,11 +9208,11 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruijff Schaal</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -8998,7 +9238,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Mundial</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -9008,7 +9248,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -9018,7 +9258,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -9028,17 +9268,17 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Johan Cruijff Schaal</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -9048,7 +9288,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -9058,17 +9298,17 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -9078,7 +9318,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -9088,15 +9328,135 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Liga Boliviana</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Copa Boliviana</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Supercopa da Itália</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F91"/>
+  <autoFilter ref="A1:F95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9107,7 +9467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11266,7 +11626,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -11382,16 +11742,16 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Supercopa da Itália</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -11412,11 +11772,11 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Eredivisie</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -11437,11 +11797,11 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Eredivisie</t>
+          <t>Melhor da Eredivisie</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -11462,11 +11822,11 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Melhor da KNVB Beker</t>
+          <t>Artilheiro da Eredivisie</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -11487,32 +11847,32 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Bola de Ouro</t>
+          <t>Melhor da KNVB Beker</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Bola de Ouro</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -11522,22 +11882,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Artilheiro da Serie A</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
@@ -11562,7 +11922,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
@@ -11587,7 +11947,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
@@ -11612,11 +11972,11 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -11637,11 +11997,11 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -11657,12 +12017,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
@@ -11682,16 +12042,16 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Melhor Jogador da Ligue 1</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -11707,12 +12067,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Melhor Jogador da Copa da França</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
@@ -11732,12 +12092,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Bola de Ouro</t>
+          <t>Supercopa da Europa</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
@@ -11747,72 +12107,72 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Melhor Jogador da Ligue 1</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Melhor Jogador da Copa da França</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
@@ -11822,26 +12182,26 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Bola de Ouro</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -11862,7 +12222,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
@@ -11887,11 +12247,11 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -11912,7 +12272,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
@@ -11937,11 +12297,11 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -11957,16 +12317,16 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -11982,12 +12342,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Melhor do Brasileirão</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
@@ -12007,12 +12367,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro do Brasileirão</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
@@ -12032,16 +12392,16 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Copa do Brasil</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -12057,16 +12417,16 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa do Brasil</t>
+          <t>Supercopa da Europa</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -12082,12 +12442,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Ligue 1</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
@@ -12112,11 +12472,11 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Ligue 1</t>
+          <t>Artilheiro da Copa Boliviana</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -12137,7 +12497,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa da França</t>
+          <t>Melhor do Brasileirão</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
@@ -12162,15 +12522,240 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
+          <t>Artilheiro do Brasileirão</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Melhor da Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Melhor da Ligue 1</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Ligue 1</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa da França</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Melhor Jogador da Copa da França</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Chuteira de Ouro</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Bola de Ouro</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
           <t>Artilheiro da Copa do Mundo</t>
         </is>
       </c>
-      <c r="E122" s="2" t="n">
+      <c r="E131" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E122"/>
+  <autoFilter ref="A1:E131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12378,28 +12963,28 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>351</v>
+        <v>404</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>351</v>
+        <v>404</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -12417,28 +13002,28 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -12456,28 +13041,28 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>

--- a/data/jogadores_carreiras.xlsx
+++ b/data/jogadores_carreiras.xlsx
@@ -18,9 +18,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Jogadores'!$A$1:$M$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conquistas Jogador'!$A$1:$E$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Checks'!$A$1:$K$7</definedName>
   </definedNames>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>404</v>
+        <v>465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>317</v>
+        <v>373</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>404</v>
+        <v>465</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>317</v>
+        <v>373</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0</v>
@@ -782,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -845,22 +845,22 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>442</v>
+        <v>539</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>442</v>
+        <v>539</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Primeiro clube — Liga e Copa Boliviana conquistadas logo de início.</t>
+          <t>Primeiro clube — Liga e Copa Bolíviana conquistadas logo de início.</t>
         </is>
       </c>
     </row>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81 jogos, Liga Boliviana conquistada e dois prêmios de melhor jogador.</t>
+          <t>81 jogos, Liga Bolíviana conquistada e dois prêmios de melhor jogador.</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Primeira experi?ncia na Serie A e Europa League italiana.</t>
+          <t>Primeira experiência na Serie A e Europa League italiana.</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-4</t>
+          <t>guarita-fonseca-barcelona-4</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2178,97 +2178,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Seleção</t>
+          <t>Clube</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>15</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
+          <t>pages/clubes/guarita-fonseca-barcelona.html</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Titular na Copa do Mundo campe? ? e a história mal come?ou.</t>
+          <t>30 jogos, 15 gols e 10 assistências no Barça.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>guarita-fonseca-bolivia-5</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar</t>
+          <t>guarita-fonseca</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Clube</t>
+          <t>Seleção</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
+          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Estreia profissional e artilharia imediata na Copa Boliviana.</t>
+          <t>Titular na Copa do Mundo campeã e a história mal começou.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2282,16 +2282,16 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2300,29 +2300,29 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-corinthians.html</t>
+          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
+          <t>Estreia profissional e artilharia imediata na Copa Bolíviana.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2354,81 +2354,135 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-marseille.html</t>
+          <t>pages/clubes/moreno-escobar-corinthians.html</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>181 gols, Champions League, Mundial e domínio completo na França.</t>
+          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>moreno-escobar</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Moreno Escobar</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Clube</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>pages/clubes/moreno-escobar-marseille.html</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>181 gols, Champions League, Mundial e domínio completo na França.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>moreno-escobar</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Moreno Escobar</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Bolívia</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Bolívia</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Seleção</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>pages/clubes/moreno-escobar-bolivia.html</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>Artilheiro da Copa do Mundo ? 13 gols no torneio que mudou tudo.</t>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa do Mundo 13 gols no torneio que mudou tudo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L28"/>
+  <autoFilter ref="A1:L29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2439,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -5033,7 +5087,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-4</t>
+          <t>guarita-fonseca-barcelona-4</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5043,28 +5097,28 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Eliminatórias</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
         <v>20</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-4</t>
+          <t>guarita-fonseca-barcelona-4</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5074,28 +5128,28 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Copa América</t>
+          <t>Copa del Rey</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-4</t>
+          <t>guarita-fonseca-barcelona-4</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5105,28 +5159,28 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Supercopa da Espanha</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-4</t>
+          <t>guarita-fonseca-barcelona-4</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5136,28 +5190,28 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-bolivia-5</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5167,28 +5221,28 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Eliminat?rias</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-bolivia-5</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5198,28 +5252,28 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Copa Am?rica</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-bolivia-5</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5229,28 +5283,28 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-bolivia-5</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5260,22 +5314,22 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -5296,23 +5350,23 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da Europa</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5322,28 +5376,28 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5353,19 +5407,19 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Coppa Italia</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>2</v>
@@ -5374,7 +5428,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5384,28 +5438,28 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5415,28 +5469,28 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Supercopa da Europa</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5446,28 +5500,28 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5477,152 +5531,152 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Coppa Italia</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Eliminatórias</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Copa América</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Guarita Fonseca</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5632,28 +5686,28 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Eliminat?rias</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5663,28 +5717,28 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Copa Am?rica</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5694,28 +5748,28 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5725,28 +5779,28 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5756,28 +5810,28 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5787,28 +5841,28 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5818,28 +5872,28 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5849,22 +5903,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
         <v>12</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -5885,17 +5939,17 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="F111" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="G111" s="2" t="n">
         <v>35</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="112">
@@ -5916,23 +5970,23 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Mundial de Clubes</t>
+          <t>Copa da Fran?a</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5942,28 +5996,28 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Supercopa da Fran?a</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5973,19 +6027,19 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>2</v>
@@ -5994,7 +6048,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -6004,146 +6058,146 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Mundial de Clubes</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>133</v>
+        <v>2</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -6164,17 +6218,17 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Mundial de Clubes</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="121">
@@ -6195,23 +6249,23 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruijff Schaal</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6221,28 +6275,28 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Eliminatórias</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6252,28 +6306,28 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Copa América</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6283,28 +6337,28 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Mundial de Clubes</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6314,28 +6368,28 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Johan Cruijff Schaal</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6345,28 +6399,28 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Eliminat?rias</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6376,28 +6430,28 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Copa Am?rica</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6407,28 +6461,28 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6438,28 +6492,28 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Sul-Americana</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>salazar-torino-3</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6469,28 +6523,28 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>salazar-torino-3</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6500,28 +6554,28 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Copa da Itália (Coppa Italia)</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>salazar-torino-3</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6531,57 +6585,212 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Sul-Americana</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
           <t>salazar-torino-3</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Salazar</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Supercopa da Itália</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="n">
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Copa da It?lia</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Supercopa da It?lia</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F133" s="2" t="n">
+      <c r="F138" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G133" s="2" t="n">
+      <c r="G138" s="2" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G133"/>
+  <autoFilter ref="A1:G138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6592,7 +6801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -8258,7 +8467,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-4</t>
+          <t>guarita-fonseca-bolivia-5</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -8912,7 +9121,7 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -8938,11 +9147,11 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Supercopa da Fran?a</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -8968,11 +9177,11 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Copa da Fran?a</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -9002,7 +9211,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -9023,16 +9232,16 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Ligue 1</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -9053,12 +9262,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Ligue 1</t>
+          <t>Supercopa da Europa</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -9088,17 +9297,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa da França</t>
+          <t>Melhor da Ligue 1</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -9108,7 +9317,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -9118,67 +9327,67 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Artilheiro da Ligue 1</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Artilheiro da Copa da Fran?a</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Melhor Jogador da Copa da Fran?a</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
@@ -9188,57 +9397,57 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Chuteira de Ouro</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Bola de Ouro</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -9248,31 +9457,31 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Salazar</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruijff Schaal</t>
+          <t>Artilheiro da Copa Boliviana</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -9298,17 +9507,17 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Mundial</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -9318,7 +9527,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -9328,17 +9537,17 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -9348,7 +9557,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -9358,17 +9567,17 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -9378,7 +9587,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -9388,7 +9597,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
@@ -9398,7 +9607,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>salazar-torino-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -9408,7 +9617,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -9418,17 +9627,17 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da Itália</t>
+          <t>Johan Cruijff Schaal</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>salazar-torino-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -9438,7 +9647,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -9448,15 +9657,285 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>salazar-bolivia-4</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Copa do Mundo</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>salazar-bolivia-4</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Bolívia</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Copa do Mundo</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Liga Boliviana</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>salazar-oriente-petrolero-1</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Copa Boliviana</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Supercopa da It?lia</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Título coletivo</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Artilheiro da Serie A</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>salazar-torino-3</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio individual</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Melhor Jogador da Serie A</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F95"/>
+  <autoFilter ref="A1:F104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11522,7 +12001,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Liga Bolíviana</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -11547,7 +12026,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Copa Bolíviana</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -11772,7 +12251,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Melhor da Liga Bolíviana</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -11922,7 +12401,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Liga Bolíviana</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
@@ -12122,7 +12601,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Boliviana</t>
+          <t>Melhor da Liga Bolíviana</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
@@ -12472,7 +12951,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Artilheiro da Copa Bolíviana</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
@@ -12963,28 +13442,28 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>404</v>
+        <v>465</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>404</v>
+        <v>465</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>317</v>
+        <v>373</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>317</v>
+        <v>373</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -13002,28 +13481,28 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -13041,28 +13520,28 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>442</v>
+        <v>539</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>442</v>
+        <v>539</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>

--- a/data/jogadores_carreiras.xlsx
+++ b/data/jogadores_carreiras.xlsx
@@ -18,9 +18,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Jogadores'!$A$1:$M$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$138</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passagens'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desempenho Competição'!$A$1:$G$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conquistas Passagem'!$A$1:$F$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conquistas Jogador'!$A$1:$E$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Checks'!$A$1:$K$7</definedName>
   </definedNames>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>465</v>
+        <v>404</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>325</v>
+        <v>267</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>465</v>
+        <v>404</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>325</v>
+        <v>267</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0</v>
@@ -782,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -845,22 +845,22 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>378</v>
+        <v>316</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>539</v>
+        <v>442</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>378</v>
+        <v>316</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>539</v>
+        <v>442</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Primeiro clube — Liga e Copa Bolíviana conquistadas logo de início.</t>
+          <t>Primeiro clube — Liga e Copa Boliviana conquistadas logo de início.</t>
         </is>
       </c>
     </row>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81 jogos, Liga Bolíviana conquistada e dois prêmios de melhor jogador.</t>
+          <t>81 jogos, Liga Boliviana conquistada e dois prêmios de melhor jogador.</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Primeira experiência na Serie A e Europa League italiana.</t>
+          <t>Primeira experi?ncia na Serie A e Europa League italiana.</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-barcelona-4</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2178,97 +2178,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Clube</t>
+          <t>Seleção</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>15</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-barcelona.html</t>
+          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30 jogos, 15 gols e 10 assistências no Barça.</t>
+          <t>Titular na Copa do Mundo campe? ? e a história mal come?ou.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-5</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca</t>
+          <t>moreno-escobar</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Clube</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Bolívia</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Bolívia</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Seleção</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>28</v>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/guarita-fonseca-bolivia.html</t>
+          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Titular na Copa do Mundo campeã e a história mal começou.</t>
+          <t>Estreia profissional e artilharia imediata na Copa Boliviana.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2282,16 +2282,16 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2300,29 +2300,29 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-the-strongest.html</t>
+          <t>pages/clubes/moreno-escobar-corinthians.html</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Estreia profissional e artilharia imediata na Copa Bolíviana.</t>
+          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2354,29 +2354,29 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-corinthians.html</t>
+          <t>pages/clubes/moreno-escobar-marseille.html</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>175 gols em duas temporadas e quatro prêmios individuais.</t>
+          <t>181 gols, Champions League, Mundial e domínio completo na França.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2390,99 +2390,45 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Clube</t>
+          <t>Seleção</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>204</v>
+        <v>44</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>272</v>
+        <v>36</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>pages/clubes/moreno-escobar-marseille.html</t>
+          <t>pages/clubes/moreno-escobar-bolivia.html</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>181 gols, Champions League, Mundial e domínio completo na França.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>moreno-escobar-bolivia-4</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>moreno-escobar</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Moreno Escobar</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Bolívia</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Bolívia</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Seleção</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>pages/clubes/moreno-escobar-bolivia.html</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Artilheiro da Copa do Mundo 13 gols no torneio que mudou tudo.</t>
+          <t>Artilheiro da Copa do Mundo ? 13 gols no torneio que mudou tudo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L29"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2493,7 +2439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -5087,7 +5033,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-barcelona-4</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5097,28 +5043,28 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eliminatórias</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
         <v>20</v>
       </c>
       <c r="F84" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G84" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-barcelona-4</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5128,28 +5074,28 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Copa del Rey</t>
+          <t>Copa América</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F85" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G85" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-barcelona-4</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5159,28 +5105,28 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da Espanha</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-barcelona-4</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5190,28 +5136,28 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-5</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5221,28 +5167,28 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Eliminat?rias</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-5</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5252,28 +5198,28 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Copa Am?rica</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-5</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5283,28 +5229,28 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-5</t>
+          <t>guarita-fonseca-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5314,22 +5260,22 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -5350,23 +5296,23 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Supercopa da Europa</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5376,28 +5322,28 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Copa da França</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5407,19 +5353,19 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da França</t>
+          <t>Coppa Italia</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>2</v>
@@ -5428,7 +5374,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-napoli-2</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5438,28 +5384,28 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-olympique-de-marseille-3</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5469,28 +5415,28 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da Europa</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5500,28 +5446,28 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>guarita-fonseca-nacional-de-potosi-1</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5531,152 +5477,152 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Nacional de Potosí</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Coppa Italia</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G98" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-napoli-2</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Eliminatórias</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Copa América</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-nacional-de-potosi-1</t>
+          <t>moreno-escobar-bolivia-4</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Guarita Fonseca</t>
+          <t>Moreno Escobar</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Nacional de Potosí</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F102" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G102" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5686,28 +5632,28 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Eliminat?rias</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5717,28 +5663,28 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Copa Am?rica</t>
+          <t>Copa do Brasil</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5748,28 +5694,28 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Supercopa Rei</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-bolivia-4</t>
+          <t>moreno-escobar-corinthians-2</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5779,28 +5725,28 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5810,28 +5756,28 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Brasileirão</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5841,28 +5787,28 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Copa do Brasil</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5872,28 +5818,28 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Supercopa Rei</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-corinthians-2</t>
+          <t>moreno-escobar-olympique-de-marseille-3</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5903,22 +5849,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique de Marseille</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
         <v>12</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -5939,17 +5885,17 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
@@ -5970,23 +5916,23 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Copa da Fran?a</t>
+          <t>Mundial de Clubes</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5996,28 +5942,28 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da Fran?a</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -6027,19 +5973,19 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>2</v>
@@ -6048,7 +5994,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -6058,146 +6004,146 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Mundial de Clubes</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>2</v>
+        <v>133</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G117" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
@@ -6218,17 +6164,17 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Mundial de Clubes</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -6249,23 +6195,23 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Johan Cruijff Schaal</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6275,28 +6221,28 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Eliminatórias</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6306,28 +6252,28 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Copa América</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6337,28 +6283,28 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Mundial de Clubes</t>
+          <t>Amistosos</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6368,28 +6314,28 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruijff Schaal</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6399,28 +6345,28 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Eliminat?rias</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6430,28 +6376,28 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Copa Am?rica</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6461,28 +6407,28 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Amistosos</t>
+          <t>Libertadores</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>salazar-bolivia-4</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6492,28 +6438,28 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Bolívia</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Copa do Mundo</t>
+          <t>Sul-Americana</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-torino-3</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6523,28 +6469,28 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Copa Boliviana</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-torino-3</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6554,28 +6500,28 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Liga Boliviana</t>
+          <t>Copa da Itália (Coppa Italia)</t>
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-torino-3</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6585,28 +6531,28 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Libertadores</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G132" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>salazar-oriente-petrolero-1</t>
+          <t>salazar-torino-3</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6616,181 +6562,26 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Sul-Americana</t>
+          <t>Supercopa da Itália</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Copa da It?lia</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Champions League</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Supercopa da It?lia</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="2" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G138"/>
+  <autoFilter ref="A1:G133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6801,7 +6592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -8467,7 +8258,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>guarita-fonseca-bolivia-5</t>
+          <t>guarita-fonseca-bolivia-4</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9121,7 +8912,7 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -9147,11 +8938,11 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da Fran?a</t>
+          <t>Supercopa da França</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -9177,11 +8968,11 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Copa da Fran?a</t>
+          <t>Copa da França</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -9211,7 +9002,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -9232,16 +9023,16 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Mundial</t>
+          <t>Melhor da Ligue 1</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -9262,12 +9053,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Título coletivo</t>
+          <t>Prêmio individual</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Supercopa da Europa</t>
+          <t>Artilheiro da Ligue 1</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -9297,17 +9088,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Ligue 1</t>
+          <t>Artilheiro da Copa da França</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>moreno-escobar-the-strongest-1</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -9317,7 +9108,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -9327,67 +9118,67 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Ligue 1</t>
+          <t>Artilheiro da Copa Boliviana</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa da Fran?a</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Melhor Jogador da Copa da Fran?a</t>
+          <t>KNVB Beker</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
@@ -9397,57 +9188,57 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Chuteira de Ouro</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-olympique-de-marseille-3</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Olympique de Marseille</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Bola de Ouro</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -9457,31 +9248,31 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>moreno-escobar-the-strongest-1</t>
+          <t>salazar-ajax-2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Moreno Escobar</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Prêmio individual</t>
+          <t>Título coletivo</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Boliviana</t>
+          <t>Johan Cruijff Schaal</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -9507,17 +9298,17 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-bolivia-4</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -9527,7 +9318,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bolívia</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -9537,17 +9328,17 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KNVB Beker</t>
+          <t>Copa do Mundo</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -9557,7 +9348,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -9567,17 +9358,17 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-oriente-petrolero-1</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -9587,7 +9378,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -9597,7 +9388,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
@@ -9607,7 +9398,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-torino-3</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -9617,7 +9408,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -9627,17 +9418,17 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruijff Schaal</t>
+          <t>Supercopa da Itália</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>salazar-ajax-2</t>
+          <t>salazar-torino-3</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -9647,7 +9438,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -9657,285 +9448,15 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Mundial</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>salazar-bolivia-4</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Bolívia</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Título coletivo</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>Copa do Mundo</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>salazar-bolivia-4</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Bolívia</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Prêmio individual</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Artilheiro da Copa do Mundo</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>salazar-oriente-petrolero-1</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Título coletivo</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Liga Boliviana</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>salazar-oriente-petrolero-1</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Título coletivo</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Copa Boliviana</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Título coletivo</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Supercopa da It?lia</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Título coletivo</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Título coletivo</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Prêmio individual</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Artilheiro da Serie A</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>salazar-torino-3</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Prêmio individual</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Melhor Jogador da Serie A</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F104"/>
+  <autoFilter ref="A1:F95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12001,7 +11522,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Liga Bolíviana</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -12026,7 +11547,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Copa Bolíviana</t>
+          <t>Copa Boliviana</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -12251,7 +11772,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Bolíviana</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -12401,7 +11922,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Liga Bolíviana</t>
+          <t>Liga Boliviana</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
@@ -12601,7 +12122,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Melhor da Liga Bolíviana</t>
+          <t>Melhor da Liga Boliviana</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
@@ -12951,7 +12472,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Artilheiro da Copa Bolíviana</t>
+          <t>Artilheiro da Copa Boliviana</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
@@ -13442,28 +12963,28 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>465</v>
+        <v>404</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>465</v>
+        <v>404</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>325</v>
+        <v>267</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>325</v>
+        <v>267</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -13481,28 +13002,28 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -13520,28 +13041,28 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>378</v>
+        <v>316</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>378</v>
+        <v>316</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>539</v>
+        <v>442</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>539</v>
+        <v>442</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
